--- a/samtaler-nifr.xlsx
+++ b/samtaler-nifr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dean/Library/CloudStorage/OneDrive-KøbenhavnsErhvervsakademi/Documents/ITA-2024/ITA24-1-sem/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E0AA3EF-F572-4147-87B7-2E8F89BB4693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D51847-6F86-5B40-957D-BB5337A862F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15360" yWindow="760" windowWidth="19200" windowHeight="21580" xr2:uid="{EB9B53E0-4642-9C4C-960C-03EEE1D8D337}"/>
+    <workbookView xWindow="49600" yWindow="4100" windowWidth="19200" windowHeight="21100" xr2:uid="{EB9B53E0-4642-9C4C-960C-03EEE1D8D337}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
   <si>
     <t>Linea</t>
   </si>
@@ -458,7 +458,8 @@
   <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="2" max="2" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -546,10 +547,16 @@
       <c r="A13" t="s">
         <v>12</v>
       </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">

--- a/samtaler-nifr.xlsx
+++ b/samtaler-nifr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dean/Library/CloudStorage/OneDrive-KøbenhavnsErhvervsakademi/Documents/ITA-2024/ITA24-1-sem/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D51847-6F86-5B40-957D-BB5337A862F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07A66F52-A5C8-A54A-AAF2-F9A693877ECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="49600" yWindow="4100" windowWidth="19200" windowHeight="21100" xr2:uid="{EB9B53E0-4642-9C4C-960C-03EEE1D8D337}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{EB9B53E0-4642-9C4C-960C-03EEE1D8D337}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
   <si>
     <t>Linea</t>
   </si>
@@ -498,6 +498,9 @@
       <c r="A5" t="s">
         <v>4</v>
       </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
